--- a/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_64990_completo.xlsx
+++ b/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_64990_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2ddfeb40868f42ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd1aa32337fdd4878"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    872.2469</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    873.5110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    985.5335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1030.0496</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    941.4943</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    885.1858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    758.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    782.8523</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    820.3196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_64990_completo.xlsx
+++ b/49845_Intercuenca_Medio_Huallaga/_raw_reportes_xlsx/IDConfig_64990_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd1aa32337fdd4878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4811ea0a098646ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1357.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1182.4887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    766.1722</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    745.5375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    783.0551</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    851.1352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    966.6320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1098.5884</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1373.4985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1165.5256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    826.4340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1054.5892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1162.8181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    998.5240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    878.5642</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    934.3251</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    931.7393</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    995.1870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    878.7062</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1017.6276</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1247.9580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1680.3262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1143.5613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1210.8740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1176.7207</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1840.1354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    957.3196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    731.1795</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    752.8787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    800.4452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    881.8599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    861.5694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    802.4630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    676.9929</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    690.0528</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    711.9850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    731.1795</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    752.8787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    724.3251</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    775.2271</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    767.7235</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    838.7846</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    921.5486</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1067.8225</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1392.6035</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1731.1113</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1174.1454</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    966.6425</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
